--- a/data/trans_dic/P16A03-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A03-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,78</t>
+          <t>0,91; 5,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,78</t>
+          <t>0,27; 3,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,32</t>
+          <t>0,6; 3,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 10,73</t>
+          <t>4,06; 10,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 9,79</t>
+          <t>3,31; 9,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 10,75</t>
+          <t>4,4; 10,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 10,83</t>
+          <t>5,75; 10,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,82</t>
+          <t>3,0; 6,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,36</t>
+          <t>2,54; 6,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,33</t>
+          <t>2,61; 5,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,25</t>
+          <t>3,45; 6,18</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,16</t>
+          <t>0,78; 4,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,65</t>
+          <t>0,62; 3,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,5</t>
+          <t>0,43; 2,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,51</t>
+          <t>0,41; 2,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,16</t>
+          <t>2,69; 6,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,35</t>
+          <t>3,8; 8,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,98</t>
+          <t>1,19; 3,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,88</t>
+          <t>1,59; 3,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,41</t>
+          <t>2,06; 4,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,2</t>
+          <t>2,52; 5,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,73</t>
+          <t>1,01; 2,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,71</t>
+          <t>1,18; 2,73</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,53</t>
+          <t>0,3; 3,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,23</t>
+          <t>0,59; 3,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,96</t>
+          <t>2,57; 6,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 8,45</t>
+          <t>3,22; 7,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 8,72</t>
+          <t>3,6; 8,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,05</t>
+          <t>1,75; 6,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,32</t>
+          <t>5,81; 10,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,89</t>
+          <t>2,16; 5,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,28</t>
+          <t>2,44; 5,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,45</t>
+          <t>1,1; 3,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 7,75</t>
+          <t>4,64; 7,78</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,63</t>
+          <t>1,74; 5,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,15</t>
+          <t>0,55; 3,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,19</t>
+          <t>0,54; 3,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,05</t>
+          <t>0,35; 3,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 9,41</t>
+          <t>4,72; 9,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,94; 11,82</t>
+          <t>5,97; 11,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 10,75</t>
+          <t>5,45; 10,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,61</t>
+          <t>1,01; 3,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,83</t>
+          <t>3,54; 6,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,9</t>
+          <t>3,58; 6,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,5</t>
+          <t>3,31; 6,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,9</t>
+          <t>0,93; 2,81</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,53</t>
+          <t>0,49; 5,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,5</t>
+          <t>1,6; 5,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,41</t>
+          <t>2,69; 9,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 14,74</t>
+          <t>6,05; 14,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,84</t>
+          <t>1,39; 6,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 12,08</t>
+          <t>6,65; 11,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,76</t>
+          <t>1,44; 4,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 8,36</t>
+          <t>3,8; 8,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,46</t>
+          <t>0,85; 3,5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,28</t>
+          <t>4,8; 8,24</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,0</t>
+          <t>0,68; 4,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,03</t>
+          <t>0,3; 3,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,61</t>
+          <t>1,66; 4,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 10,08</t>
+          <t>4,11; 9,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,27</t>
+          <t>2,82; 8,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,48</t>
+          <t>1,95; 6,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,55</t>
+          <t>4,97; 9,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,18</t>
+          <t>2,7; 6,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,58</t>
+          <t>1,74; 4,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,98</t>
+          <t>1,37; 4,05</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,15</t>
+          <t>3,52; 6,39</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,82</t>
+          <t>1,83; 4,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,58</t>
+          <t>0,59; 2,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,91</t>
+          <t>1,39; 3,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,03</t>
+          <t>2,84; 5,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 8,71</t>
+          <t>4,71; 8,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,72</t>
+          <t>4,83; 8,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,31</t>
+          <t>2,56; 5,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,26; 9,73</t>
+          <t>3,03; 9,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,05</t>
+          <t>3,68; 6,12</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,04; 5,24</t>
+          <t>2,94; 5,11</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,15</t>
+          <t>2,32; 4,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,35</t>
+          <t>3,59; 7,28</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,94</t>
+          <t>1,49; 3,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,6</t>
+          <t>0,27; 1,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,72</t>
+          <t>0,38; 1,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,76</t>
+          <t>2,26; 4,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,02</t>
+          <t>3,16; 6,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,16</t>
+          <t>2,34; 5,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,81</t>
+          <t>1,21; 2,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,9</t>
+          <t>2,19; 3,94</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,42</t>
+          <t>1,86; 3,49</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,22</t>
+          <t>1,61; 3,19</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,41</t>
+          <t>0,53; 1,44</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,9</t>
+          <t>1,75; 2,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,8</t>
+          <t>0,96; 1,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,72</t>
+          <t>0,97; 1,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,49</t>
+          <t>1,49; 2,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,06</t>
+          <t>4,58; 6,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,87</t>
+          <t>5,23; 6,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,88</t>
+          <t>3,46; 4,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,07; 5,65</t>
+          <t>4,08; 5,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,31; 4,24</t>
+          <t>3,35; 4,3</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,2</t>
+          <t>3,29; 4,22</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,16</t>
+          <t>2,4; 3,14</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,0</t>
+          <t>3,02; 3,97</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2813; 13162</t>
+          <t>2813; 13160</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1879; 13868</t>
+          <t>2652; 14714</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>801; 8166</t>
+          <t>802; 9661</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2241; 10347</t>
+          <t>1857; 9559</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10949; 27999</t>
+          <t>10581; 27232</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9978; 27359</t>
+          <t>9247; 26380</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12569; 31026</t>
+          <t>12709; 31380</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17191; 31358</t>
+          <t>16655; 31519</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15633; 36408</t>
+          <t>16040; 35692</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14357; 36212</t>
+          <t>14464; 35613</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15395; 36867</t>
+          <t>15230; 34787</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20643; 37571</t>
+          <t>20713; 37123</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3683; 20510</t>
+          <t>3846; 19724</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3105; 23526</t>
+          <t>3151; 20094</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2255; 12586</t>
+          <t>2185; 12643</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2029; 12995</t>
+          <t>2101; 12345</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13845; 31024</t>
+          <t>13563; 31710</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20442; 43672</t>
+          <t>19873; 42371</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6370; 20798</t>
+          <t>6202; 19685</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7901; 19942</t>
+          <t>8164; 19682</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19913; 43937</t>
+          <t>20536; 45538</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26132; 53493</t>
+          <t>25936; 54049</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10274; 27976</t>
+          <t>10358; 27315</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11720; 27934</t>
+          <t>12207; 28116</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>946; 11263</t>
+          <t>950; 11727</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1869; 10446</t>
+          <t>1894; 10575</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4823</t>
+          <t>0; 4812</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8000; 21975</t>
+          <t>8103; 21865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11090; 28326</t>
+          <t>10786; 26185</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12291; 29661</t>
+          <t>12246; 29834</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6433; 20345</t>
+          <t>5889; 20560</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20344; 36013</t>
+          <t>20298; 35278</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14286; 31984</t>
+          <t>14124; 33240</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15323; 35007</t>
+          <t>16157; 36018</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7604; 22611</t>
+          <t>7185; 22559</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32160; 51490</t>
+          <t>30830; 51715</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5991; 20190</t>
+          <t>6257; 20190</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1855; 11772</t>
+          <t>2052; 12593</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1941; 11811</t>
+          <t>2001; 11839</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1105; 12663</t>
+          <t>1108; 12337</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17464; 34946</t>
+          <t>17551; 37097</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23047; 45854</t>
+          <t>23173; 45398</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20760; 41630</t>
+          <t>21111; 42379</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4983; 17160</t>
+          <t>4809; 17319</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27656; 49846</t>
+          <t>25865; 50440</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27658; 52560</t>
+          <t>27248; 51201</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24948; 49258</t>
+          <t>25028; 49476</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8265; 22816</t>
+          <t>7353; 22116</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4250</t>
+          <t>0; 5477</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1051; 9627</t>
+          <t>1042; 11358</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4006</t>
+          <t>0; 5330</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2787; 9826</t>
+          <t>2866; 9901</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5519; 19537</t>
+          <t>5596; 19298</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13477; 32362</t>
+          <t>13295; 31243</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3060; 14953</t>
+          <t>3036; 13277</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13706; 25213</t>
+          <t>13885; 24408</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6138; 19542</t>
+          <t>5900; 19762</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16061; 36145</t>
+          <t>16413; 37534</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3717; 14880</t>
+          <t>3641; 15062</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17821; 32068</t>
+          <t>18589; 31916</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1897; 10837</t>
+          <t>1845; 11868</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7044</t>
+          <t>0; 6057</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>789; 7962</t>
+          <t>790; 8307</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4146; 12438</t>
+          <t>4466; 12818</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11595; 28042</t>
+          <t>11434; 27451</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8189; 23095</t>
+          <t>7870; 23335</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4923; 17705</t>
+          <t>5339; 18585</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12796; 24548</t>
+          <t>12773; 24418</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14966; 33948</t>
+          <t>14848; 33973</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9850; 25343</t>
+          <t>9637; 25457</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7201; 21321</t>
+          <t>7366; 21709</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18915; 32380</t>
+          <t>18529; 33654</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10963; 29643</t>
+          <t>11275; 29193</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3200; 17076</t>
+          <t>3882; 16792</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9648; 25681</t>
+          <t>9155; 26200</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17491; 37634</t>
+          <t>17710; 37380</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28978; 55591</t>
+          <t>30087; 55205</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33053; 60476</t>
+          <t>33502; 61044</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17012; 36725</t>
+          <t>17670; 37897</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>27721; 82595</t>
+          <t>25709; 82658</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>46262; 75790</t>
+          <t>46097; 76712</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>41257; 71050</t>
+          <t>39945; 69386</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30289; 55991</t>
+          <t>31332; 57259</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>53851; 108309</t>
+          <t>52834; 107222</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10905; 29253</t>
+          <t>11076; 28730</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2067; 12435</t>
+          <t>2131; 14271</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2755; 13394</t>
+          <t>2974; 13839</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 7145</t>
+          <t>0; 6903</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>17584; 37287</t>
+          <t>17741; 37310</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24578; 49419</t>
+          <t>25978; 49695</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20258; 42611</t>
+          <t>19336; 42436</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9021; 20094</t>
+          <t>8652; 20369</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>32635; 59478</t>
+          <t>33384; 60069</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>28806; 54729</t>
+          <t>29687; 55725</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25592; 51637</t>
+          <t>25764; 51203</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8875; 23139</t>
+          <t>8704; 23600</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>58615; 94985</t>
+          <t>57390; 91669</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>34073; 61591</t>
+          <t>32689; 62370</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31640; 58547</t>
+          <t>32914; 58279</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50926; 86019</t>
+          <t>51668; 87804</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>154147; 204663</t>
+          <t>154672; 206254</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>185300; 243332</t>
+          <t>185266; 243139</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>123591; 172901</t>
+          <t>122626; 175335</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>148904; 206724</t>
+          <t>149245; 208661</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>220429; 281987</t>
+          <t>222735; 286084</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>227342; 292577</t>
+          <t>228931; 294050</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>162858; 218963</t>
+          <t>166431; 217995</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>212144; 284391</t>
+          <t>215097; 282375</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A03-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A03-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,82</t>
+          <t>0,96; 4,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,07</t>
+          <t>0,91; 4,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,29</t>
+          <t>0,27; 3,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,07</t>
+          <t>0,67; 3,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 10,44</t>
+          <t>4,31; 10,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 9,44</t>
+          <t>3,32; 9,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 10,87</t>
+          <t>4,35; 10,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,75; 10,88</t>
+          <t>5,21; 9,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,69</t>
+          <t>2,93; 6,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,25</t>
+          <t>2,58; 6,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,97</t>
+          <t>2,63; 6,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,18</t>
+          <t>3,14; 5,66</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,0</t>
+          <t>0,73; 3,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,97</t>
+          <t>0,62; 4,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,52</t>
+          <t>0,45; 2,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,39</t>
+          <t>0,38; 2,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,29</t>
+          <t>2,72; 6,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,11</t>
+          <t>3,85; 8,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,76</t>
+          <t>1,06; 3,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,83</t>
+          <t>1,49; 3,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,57</t>
+          <t>2,05; 4,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,26</t>
+          <t>2,58; 5,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,66</t>
+          <t>1,01; 2,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,73</t>
+          <t>1,2; 2,67</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,68</t>
+          <t>0,3; 3,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,27</t>
+          <t>0,59; 3,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,93</t>
+          <t>2,58; 6,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 7,81</t>
+          <t>3,39; 8,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 8,78</t>
+          <t>3,47; 8,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,11</t>
+          <t>1,81; 6,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,1</t>
+          <t>5,76; 10,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,08</t>
+          <t>2,07; 5,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,43</t>
+          <t>2,41; 5,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,44</t>
+          <t>1,03; 3,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,78</t>
+          <t>4,62; 7,71</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,63</t>
+          <t>1,66; 5,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,37</t>
+          <t>0,56; 3,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,2</t>
+          <t>0,53; 3,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,95</t>
+          <t>0,31; 3,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 9,99</t>
+          <t>4,49; 9,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 11,7</t>
+          <t>5,8; 11,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,94</t>
+          <t>5,04; 10,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,64</t>
+          <t>1,71; 4,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,91</t>
+          <t>3,71; 6,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,72</t>
+          <t>3,44; 6,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,53</t>
+          <t>3,3; 6,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,81</t>
+          <t>1,22; 3,28</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,34</t>
+          <t>0,48; 4,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,54</t>
+          <t>1,36; 5,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,29</t>
+          <t>2,68; 9,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 14,23</t>
+          <t>6,09; 15,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,07</t>
+          <t>1,29; 6,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,65; 11,7</t>
+          <t>5,87; 10,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,81</t>
+          <t>1,46; 5,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,68</t>
+          <t>3,39; 8,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,5</t>
+          <t>0,87; 3,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 8,24</t>
+          <t>4,2; 7,14</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,38</t>
+          <t>0,68; 3,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,16</t>
+          <t>0,3; 2,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,75</t>
+          <t>1,62; 4,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,11; 9,87</t>
+          <t>3,95; 9,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,36</t>
+          <t>2,93; 8,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,8</t>
+          <t>1,85; 6,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,5</t>
+          <t>4,64; 9,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,19</t>
+          <t>2,57; 6,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,6</t>
+          <t>1,63; 4,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,05</t>
+          <t>1,35; 3,99</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,39</t>
+          <t>3,57; 6,27</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,75</t>
+          <t>1,75; 4,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,53</t>
+          <t>0,56; 2,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,99</t>
+          <t>1,45; 3,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,99</t>
+          <t>3,3; 6,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,65</t>
+          <t>4,72; 8,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,8</t>
+          <t>4,77; 8,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,48</t>
+          <t>2,39; 5,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 9,73</t>
+          <t>7,71; 11,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,12</t>
+          <t>3,67; 6,04</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,11</t>
+          <t>2,92; 5,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,25</t>
+          <t>2,25; 4,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,28</t>
+          <t>6,05; 8,8</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,87</t>
+          <t>1,51; 3,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,84</t>
+          <t>0,28; 1,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,78</t>
+          <t>0,37; 1,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,76</t>
+          <t>2,23; 4,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,05</t>
+          <t>2,94; 5,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,14</t>
+          <t>2,35; 5,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,85</t>
+          <t>1,21; 2,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,94</t>
+          <t>2,15; 3,81</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,49</t>
+          <t>1,84; 3,41</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,19</t>
+          <t>1,64; 3,2</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,44</t>
+          <t>0,68; 1,52</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,8</t>
+          <t>1,74; 2,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,82</t>
+          <t>0,93; 1,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,72</t>
+          <t>0,94; 1,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,54</t>
+          <t>1,7; 2,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,1</t>
+          <t>4,52; 6,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,86</t>
+          <t>5,22; 6,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,95</t>
+          <t>3,48; 4,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,7</t>
+          <t>4,78; 6,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,35; 4,3</t>
+          <t>3,37; 4,37</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,22</t>
+          <t>3,26; 4,22</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,14</t>
+          <t>2,39; 3,16</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,02; 3,97</t>
+          <t>3,43; 4,24</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23327</t>
+          <t>22728</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28134</t>
+          <t>27413</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2813; 13160</t>
+          <t>2627; 13272</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2652; 14714</t>
+          <t>2638; 14071</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>802; 9661</t>
+          <t>795; 9296</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1857; 9559</t>
+          <t>2125; 9784</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10581; 27232</t>
+          <t>11231; 28380</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9247; 26380</t>
+          <t>9285; 27212</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12709; 31380</t>
+          <t>12561; 31281</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16655; 31519</t>
+          <t>16461; 30483</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16040; 35692</t>
+          <t>15620; 36315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14464; 35613</t>
+          <t>14680; 35375</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15230; 34787</t>
+          <t>15313; 36065</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20713; 37123</t>
+          <t>19929; 35959</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13001</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18452</t>
+          <t>19557</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3846; 19724</t>
+          <t>3588; 19124</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3151; 20094</t>
+          <t>3145; 20481</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2185; 12643</t>
+          <t>2238; 12569</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2101; 12345</t>
+          <t>2029; 12028</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13563; 31710</t>
+          <t>13718; 32053</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19873; 42371</t>
+          <t>20132; 42784</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6202; 19685</t>
+          <t>5547; 19317</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8164; 19682</t>
+          <t>8134; 21024</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20536; 45538</t>
+          <t>20418; 44336</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25936; 54049</t>
+          <t>26527; 56616</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10358; 27315</t>
+          <t>10396; 26902</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12207; 28116</t>
+          <t>12879; 28740</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27107</t>
+          <t>27481</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40582</t>
+          <t>40438</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>950; 11727</t>
+          <t>945; 11343</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1894; 10575</t>
+          <t>1895; 11527</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4812</t>
+          <t>0; 5551</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8103; 21865</t>
+          <t>8147; 21484</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10786; 26185</t>
+          <t>11355; 28099</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12246; 29834</t>
+          <t>11793; 29366</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5889; 20560</t>
+          <t>6074; 20567</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20298; 35278</t>
+          <t>20523; 36371</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14124; 33240</t>
+          <t>13528; 32823</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16157; 36018</t>
+          <t>16011; 35827</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7185; 22559</t>
+          <t>6765; 22582</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30830; 51715</t>
+          <t>31042; 51790</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>15819</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6257; 20190</t>
+          <t>5956; 18481</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2052; 12593</t>
+          <t>2078; 11823</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2001; 11839</t>
+          <t>1945; 11417</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1108; 12337</t>
+          <t>1154; 11397</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17551; 37097</t>
+          <t>16666; 36610</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23173; 45398</t>
+          <t>22506; 46457</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21111; 42379</t>
+          <t>19513; 41801</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4809; 17319</t>
+          <t>7216; 19975</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25865; 50440</t>
+          <t>27103; 50185</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27248; 51201</t>
+          <t>26235; 51993</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25028; 49476</t>
+          <t>25000; 48651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7353; 22116</t>
+          <t>9658; 26061</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24113</t>
+          <t>23861</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5477</t>
+          <t>0; 5395</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1042; 11358</t>
+          <t>1030; 10332</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5330</t>
+          <t>0; 5405</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2866; 9901</t>
+          <t>2794; 10970</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5596; 19298</t>
+          <t>5572; 19070</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13295; 31243</t>
+          <t>13375; 33329</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3036; 13277</t>
+          <t>2823; 13791</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13885; 24408</t>
+          <t>13332; 23577</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5900; 19762</t>
+          <t>5993; 20572</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16413; 37534</t>
+          <t>14646; 35994</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3641; 15062</t>
+          <t>3724; 14539</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18589; 31916</t>
+          <t>18196; 30926</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17561</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25127</t>
+          <t>25071</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1845; 11868</t>
+          <t>1836; 10576</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6057</t>
+          <t>0; 6122</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>790; 8307</t>
+          <t>783; 7550</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4466; 12818</t>
+          <t>4398; 12878</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11434; 27451</t>
+          <t>10990; 27305</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7870; 23335</t>
+          <t>8193; 23776</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5339; 18585</t>
+          <t>5061; 17811</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12773; 24418</t>
+          <t>12231; 23733</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14848; 33973</t>
+          <t>14110; 33086</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9637; 25457</t>
+          <t>8990; 24895</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7366; 21709</t>
+          <t>7219; 21385</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18529; 33654</t>
+          <t>19058; 33518</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26415</t>
+          <t>34611</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>58118</t>
+          <t>73210</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>84533</t>
+          <t>107821</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11275; 29193</t>
+          <t>10774; 29636</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3882; 16792</t>
+          <t>3703; 16996</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9155; 26200</t>
+          <t>9511; 26005</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17710; 37380</t>
+          <t>23716; 48291</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30087; 55205</t>
+          <t>30126; 55741</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33502; 61044</t>
+          <t>33127; 60434</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17670; 37897</t>
+          <t>16524; 36710</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>25709; 82658</t>
+          <t>59563; 90776</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>46097; 76712</t>
+          <t>45984; 75710</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39945; 69386</t>
+          <t>39601; 69226</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31332; 57259</t>
+          <t>30275; 57655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>52834; 107222</t>
+          <t>90191; 131346</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>13663</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>17195</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>11076; 28730</t>
+          <t>11208; 27936</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2131; 14271</t>
+          <t>2166; 12591</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2974; 13839</t>
+          <t>2871; 13561</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 6903</t>
+          <t>0; 6047</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>17741; 37310</t>
+          <t>17462; 38280</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25978; 49695</t>
+          <t>24193; 48836</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19336; 42436</t>
+          <t>19430; 41268</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8652; 20369</t>
+          <t>10013; 22022</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>33384; 60069</t>
+          <t>32872; 58221</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>29687; 55725</t>
+          <t>29336; 54533</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25764; 51203</t>
+          <t>26286; 51403</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8704; 23600</t>
+          <t>11029; 24749</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>68876</t>
+          <t>77041</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>181169</t>
+          <t>200134</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>250045</t>
+          <t>277175</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>57390; 91669</t>
+          <t>56909; 93723</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>32689; 62370</t>
+          <t>31896; 62408</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>32914; 58279</t>
+          <t>32060; 56894</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51668; 87804</t>
+          <t>60192; 93936</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>154672; 206254</t>
+          <t>152853; 207030</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>185266; 243139</t>
+          <t>184917; 244436</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>122626; 175335</t>
+          <t>123306; 171513</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>149245; 208661</t>
+          <t>178432; 226139</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>222735; 286084</t>
+          <t>224272; 290756</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>228931; 294050</t>
+          <t>227027; 293901</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>166431; 217995</t>
+          <t>165567; 219283</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>215097; 282375</t>
+          <t>249208; 307629</t>
         </is>
       </c>
     </row>
